--- a/dataSheet/getDataExcel.xlsx
+++ b/dataSheet/getDataExcel.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="550">
   <si>
     <t>Actual Project Name</t>
   </si>
@@ -1627,6 +1627,45 @@
   </si>
   <si>
     <t>FireFlink_72366</t>
+  </si>
+  <si>
+    <t>FireFlink_69421</t>
+  </si>
+  <si>
+    <t>FireFlink_87718</t>
+  </si>
+  <si>
+    <t>FireFlink_32001</t>
+  </si>
+  <si>
+    <t>FireFlink_26934</t>
+  </si>
+  <si>
+    <t>FireFlink_40594</t>
+  </si>
+  <si>
+    <t>FireFlink_60529</t>
+  </si>
+  <si>
+    <t>FireFlink_09216</t>
+  </si>
+  <si>
+    <t>FireFlink_21456</t>
+  </si>
+  <si>
+    <t>FireFlink_43836</t>
+  </si>
+  <si>
+    <t>FireFlink_78112</t>
+  </si>
+  <si>
+    <t>FireFlink_83442</t>
+  </si>
+  <si>
+    <t>FireFlink_88660</t>
+  </si>
+  <si>
+    <t>FireFlink_86255</t>
   </si>
 </sst>
 </file>
@@ -1995,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
     </row>
   </sheetData>
